--- a/diseases/d094/2000-2004.xlsx
+++ b/diseases/d094/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>888</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>17.15543724485996</v>
       </c>
@@ -1935,9 +1932,6 @@
       <c r="O8" t="n">
         <v>923</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>17.83160875788935</v>
       </c>
@@ -2718,9 +2712,6 @@
       <c r="O12" t="n">
         <v>969</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>18.72029131787084</v>
       </c>
@@ -3501,9 +3492,6 @@
       <c r="O16" t="n">
         <v>767</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>14.81781572838693</v>
       </c>
@@ -4284,9 +4272,6 @@
       <c r="O20" t="n">
         <v>967</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>18.68165294569773</v>
       </c>
@@ -5067,9 +5052,6 @@
       <c r="O24" t="n">
         <v>880</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>17.00088375616753</v>
       </c>
@@ -5850,9 +5832,6 @@
       <c r="O28" t="n">
         <v>973</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>18.79756806221705</v>
       </c>
@@ -6633,9 +6612,6 @@
       <c r="O32" t="n">
         <v>1146</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>22.1397872551909</v>
       </c>
@@ -7416,9 +7392,6 @@
       <c r="O36" t="n">
         <v>1159</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>22.3909366743161</v>
       </c>
@@ -8199,9 +8172,6 @@
       <c r="O40" t="n">
         <v>1100</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>21.25110469520941</v>
       </c>
@@ -8982,9 +8952,6 @@
       <c r="O44" t="n">
         <v>1083</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>20.92267853173799</v>
       </c>
@@ -9765,9 +9732,6 @@
       <c r="O48" t="n">
         <v>874</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>16.8849686396482</v>
       </c>
@@ -10548,9 +10512,6 @@
       <c r="O52" t="n">
         <v>1187</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>22.87985033069769</v>
       </c>
@@ -11570,9 +11531,6 @@
       <c r="O57" t="n">
         <v>902</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>17.38637320833135</v>
       </c>
@@ -12353,9 +12311,6 @@
       <c r="O61" t="n">
         <v>912</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>17.57912679157227</v>
       </c>
@@ -13136,9 +13091,6 @@
       <c r="O65" t="n">
         <v>987</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>19.0247786658792</v>
       </c>
@@ -13919,9 +13871,6 @@
       <c r="O69" t="n">
         <v>1119</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>21.5691259646594</v>
       </c>
@@ -14702,9 +14651,6 @@
       <c r="O73" t="n">
         <v>788</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>15.18898235938481</v>
       </c>
@@ -15485,9 +15431,6 @@
       <c r="O77" t="n">
         <v>880</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>16.96231532520132</v>
       </c>
@@ -16268,9 +16211,6 @@
       <c r="O81" t="n">
         <v>1213</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>23.38100964712409</v>
       </c>
@@ -17051,9 +16991,6 @@
       <c r="O85" t="n">
         <v>1084</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>20.89448842331617</v>
       </c>
@@ -17834,9 +17771,6 @@
       <c r="O89" t="n">
         <v>1160</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>22.35941565594719</v>
       </c>
@@ -18617,9 +18551,6 @@
       <c r="O93" t="n">
         <v>1140</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>21.97390848946534</v>
       </c>
@@ -19400,9 +19331,6 @@
       <c r="O97" t="n">
         <v>769</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>14.82275055122706</v>
       </c>
@@ -20183,9 +20111,6 @@
       <c r="O101" t="n">
         <v>1300</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>24.99737527559606</v>
       </c>
@@ -21205,9 +21130,6 @@
       <c r="O106" t="n">
         <v>1104</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>21.22854023404466</v>
       </c>
@@ -21988,9 +21910,6 @@
       <c r="O110" t="n">
         <v>981</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>18.86340395796903</v>
       </c>
@@ -22771,9 +22690,6 @@
       <c r="O114" t="n">
         <v>1103</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>21.20931148383266</v>
       </c>
@@ -23554,9 +23470,6 @@
       <c r="O118" t="n">
         <v>1266</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>24.34359776838816</v>
       </c>
@@ -24337,9 +24250,6 @@
       <c r="O122" t="n">
         <v>952</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>18.30577020182112</v>
       </c>
@@ -25120,9 +25030,6 @@
       <c r="O126" t="n">
         <v>1159</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>22.28612149570449</v>
       </c>
@@ -25903,9 +25810,6 @@
       <c r="O130" t="n">
         <v>1294</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>24.88200277432408</v>
       </c>
@@ -26686,9 +26590,6 @@
       <c r="O134" t="n">
         <v>1189</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>22.8629840020644</v>
       </c>
@@ -27469,9 +27370,6 @@
       <c r="O138" t="n">
         <v>1290</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>24.8050877734761</v>
       </c>
@@ -28252,9 +28150,6 @@
       <c r="O142" t="n">
         <v>1091</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>20.97856648128869</v>
       </c>
@@ -29035,9 +28930,6 @@
       <c r="O146" t="n">
         <v>934</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>17.95965269800517</v>
       </c>
@@ -29818,9 +29710,6 @@
       <c r="O150" t="n">
         <v>1217</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>23.34568397386895</v>
       </c>
@@ -30840,9 +30729,6 @@
       <c r="O155" t="n">
         <v>1009</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>19.35562459296119</v>
       </c>
@@ -31623,9 +31509,6 @@
       <c r="O159" t="n">
         <v>1072</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>20.56415219390921</v>
       </c>
@@ -32406,9 +32289,6 @@
       <c r="O163" t="n">
         <v>939</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>18.01281614746339</v>
       </c>
@@ -33189,9 +33069,6 @@
       <c r="O167" t="n">
         <v>1054</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>20.21885859363835</v>
       </c>
@@ -33972,9 +33849,6 @@
       <c r="O171" t="n">
         <v>941</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>18.05118210304904</v>
       </c>
@@ -34755,9 +34629,6 @@
       <c r="O175" t="n">
         <v>1018</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>19.52827139309662</v>
       </c>
@@ -35538,9 +35409,6 @@
       <c r="O179" t="n">
         <v>1211</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>23.23058610711199</v>
       </c>
@@ -36321,9 +36189,6 @@
       <c r="O183" t="n">
         <v>1211</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>23.23058610711199</v>
       </c>
@@ -37104,9 +36969,6 @@
       <c r="O187" t="n">
         <v>1193</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>22.88529250684113</v>
       </c>
@@ -37887,9 +37749,6 @@
       <c r="O191" t="n">
         <v>1036</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>19.87356499336748</v>
       </c>
@@ -38670,9 +38529,6 @@
       <c r="O195" t="n">
         <v>965</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>18.51157357007686</v>
       </c>
@@ -39453,9 +39309,6 @@
       <c r="O199" t="n">
         <v>1107</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>21.17384588194519</v>
       </c>
@@ -40475,9 +40328,6 @@
       <c r="O204" t="n">
         <v>1057</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>20.21748427932798</v>
       </c>
@@ -41258,9 +41108,6 @@
       <c r="O208" t="n">
         <v>1186</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>22.6848972140804</v>
       </c>
@@ -42041,9 +41888,6 @@
       <c r="O212" t="n">
         <v>1030</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>19.70104901391468</v>
       </c>
@@ -42824,9 +42668,6 @@
       <c r="O216" t="n">
         <v>1068</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>20.42788383190377</v>
       </c>
@@ -43607,9 +43448,6 @@
       <c r="O220" t="n">
         <v>1066</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>20.38962936779907</v>
       </c>
@@ -44390,9 +44228,6 @@
       <c r="O224" t="n">
         <v>1076</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>20.58090168832252</v>
       </c>
@@ -45173,9 +45008,6 @@
       <c r="O228" t="n">
         <v>1218</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>23.29696863975542</v>
       </c>
@@ -45956,9 +45788,6 @@
       <c r="O232" t="n">
         <v>1259</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>24.08118515390153</v>
       </c>
@@ -46739,9 +46568,6 @@
       <c r="O236" t="n">
         <v>1103</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>21.09733695373582</v>
       </c>
@@ -47522,9 +47348,6 @@
       <c r="O240" t="n">
         <v>1208</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>23.10569631923197</v>
       </c>
@@ -48304,9 +48127,6 @@
       </c>
       <c r="O244" t="n">
         <v>1000</v>
-      </c>
-      <c r="Q244" t="n">
-        <v>0</v>
       </c>
       <c r="R244" t="n">
         <v>19.12723205234435</v>
